--- a/artfynd/A 33041-2024 artfynd.xlsx
+++ b/artfynd/A 33041-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56824048</v>
+        <v>6771509</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646054.0751639165</v>
+        <v>646638</v>
       </c>
       <c r="R2" t="n">
-        <v>7102027.117234118</v>
+        <v>7101871</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,76 +770,61 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56824056</v>
+        <v>96497720</v>
       </c>
       <c r="B3" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>816</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646054.2063059129</v>
+        <v>645986</v>
       </c>
       <c r="R3" t="n">
-        <v>7102146.142065343</v>
+        <v>7102091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,26 +867,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>silverstubbe tall</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -922,12 +886,7 @@
         <v>56824049</v>
       </c>
       <c r="B4" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646026.8143005471</v>
+        <v>646027</v>
       </c>
       <c r="R4" t="n">
-        <v>7101980.161839934</v>
+        <v>7101980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +951,9 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56824059</v>
+        <v>96497749</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,34 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646072.004194882</v>
+        <v>645866</v>
       </c>
       <c r="R5" t="n">
-        <v>7102169.814383704</v>
+        <v>7102074</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,22 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,62 +1072,52 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>kolad tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56824051</v>
+        <v>61489442</v>
       </c>
       <c r="B6" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>645892.7769449747</v>
+        <v>646221</v>
       </c>
       <c r="R6" t="n">
-        <v>7101903.164568469</v>
+        <v>7102133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,22 +1157,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,76 +1173,61 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Per Nihlén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56824061</v>
+        <v>96497719</v>
       </c>
       <c r="B7" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646091.8928085146</v>
+        <v>645993</v>
       </c>
       <c r="R7" t="n">
-        <v>7102195.780639576</v>
+        <v>7102087</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,22 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,76 +1270,61 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>silverstubbe tall</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56824060</v>
+        <v>96497728</v>
       </c>
       <c r="B8" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646091.8928085146</v>
+        <v>646058</v>
       </c>
       <c r="R8" t="n">
-        <v>7102195.780639576</v>
+        <v>7101984</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,22 +1351,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,76 +1367,61 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>silverstubbe tall</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56824050</v>
+        <v>96497737</v>
       </c>
       <c r="B9" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>645892.7769449747</v>
+        <v>645896</v>
       </c>
       <c r="R9" t="n">
-        <v>7101903.164568469</v>
+        <v>7101956</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,22 +1448,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,76 +1464,61 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56824055</v>
+        <v>96497739</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>645679.2091027095</v>
+        <v>645862</v>
       </c>
       <c r="R10" t="n">
-        <v>7102021.845733065</v>
+        <v>7101950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,22 +1545,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,76 +1561,61 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56824052</v>
+        <v>96497748</v>
       </c>
       <c r="B11" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>645866.9281800679</v>
+        <v>645860</v>
       </c>
       <c r="R11" t="n">
-        <v>7101901.074653818</v>
+        <v>7102071</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,22 +1642,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,41 +1658,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>56824058</v>
+        <v>62890461</v>
       </c>
       <c r="B12" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,21 +1685,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1935,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646072.004194882</v>
+        <v>646234</v>
       </c>
       <c r="R12" t="n">
-        <v>7102169.814383704</v>
+        <v>7102090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,22 +1739,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,41 +1755,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Sören Uppsäll, Per Nihlén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56824053</v>
+        <v>61489428</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,21 +1782,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2057,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>645835.7908433678</v>
+        <v>646234</v>
       </c>
       <c r="R13" t="n">
-        <v>7101871.067031531</v>
+        <v>7102090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,22 +1836,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,41 +1852,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Per Nihlén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>56824057</v>
+        <v>61489443</v>
       </c>
       <c r="B14" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,21 +1879,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2179,10 +1903,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>646054.2063059129</v>
+        <v>646187</v>
       </c>
       <c r="R14" t="n">
-        <v>7102146.142065343</v>
+        <v>7102124</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2209,22 +1933,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2235,41 +1949,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>silverstubbe tall</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Per Nihlén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96497731</v>
+        <v>96497724</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,21 +1976,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2301,10 +2000,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>646027.7319903609</v>
+        <v>646037</v>
       </c>
       <c r="R15" t="n">
-        <v>7101923.108659576</v>
+        <v>7102069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2334,19 +2033,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2373,15 +2062,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96497751</v>
+        <v>96497726</v>
       </c>
       <c r="B16" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2073,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2413,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>645869.5408444846</v>
+        <v>646059</v>
       </c>
       <c r="R16" t="n">
-        <v>7102108.056560005</v>
+        <v>7102006</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,21 +2130,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2469,11 +2143,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2490,15 +2159,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96497732</v>
+        <v>96497741</v>
       </c>
       <c r="B17" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,21 +2170,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2530,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>646016.1925558809</v>
+        <v>645885</v>
       </c>
       <c r="R17" t="n">
-        <v>7101915.979195877</v>
+        <v>7101965</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2563,21 +2227,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2586,11 +2240,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2607,50 +2256,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96497741</v>
+        <v>61489444</v>
       </c>
       <c r="B18" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>645884.5944067793</v>
+        <v>646167</v>
       </c>
       <c r="R18" t="n">
-        <v>7101965.14774894</v>
+        <v>7102103</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2677,22 +2321,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,27 +2341,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+          <t>Per Nihlén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96497739</v>
+        <v>96497753</v>
       </c>
       <c r="B19" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2735,21 +2364,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2759,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>645861.556291086</v>
+        <v>645912</v>
       </c>
       <c r="R19" t="n">
-        <v>7101950.013647038</v>
+        <v>7102113</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2792,19 +2421,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2831,15 +2450,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96497752</v>
+        <v>61489441</v>
       </c>
       <c r="B20" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,34 +2461,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>645869.5408444846</v>
+        <v>646222</v>
       </c>
       <c r="R20" t="n">
-        <v>7102108.056560005</v>
+        <v>7102130</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2901,22 +2515,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2927,71 +2531,61 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+          <t>Per Nihlén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96497734</v>
+        <v>56824048</v>
       </c>
       <c r="B21" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>645942.7131838608</v>
+        <v>646054</v>
       </c>
       <c r="R21" t="n">
-        <v>7101926.148293816</v>
+        <v>7102027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3018,22 +2612,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3045,39 +2629,39 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96497725</v>
+        <v>56824055</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3101,14 +2685,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>646071.8668280735</v>
+        <v>645679</v>
       </c>
       <c r="R22" t="n">
-        <v>7102013.458834261</v>
+        <v>7102022</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3135,22 +2719,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3161,66 +2735,71 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96497735</v>
+        <v>61489440</v>
       </c>
       <c r="B23" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>645942.7131838608</v>
+        <v>646229</v>
       </c>
       <c r="R23" t="n">
-        <v>7101926.148293816</v>
+        <v>7102082</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3247,22 +2826,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3273,58 +2842,48 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>tallstubbe</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+          <t>Per Nihlén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96497727</v>
+        <v>96497718</v>
       </c>
       <c r="B24" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3334,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>646057.6744867433</v>
+        <v>645956</v>
       </c>
       <c r="R24" t="n">
-        <v>7102006.644065643</v>
+        <v>7102101</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3367,21 +2926,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3390,11 +2939,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>tallstubbe</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3411,37 +2955,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96497737</v>
+        <v>96497725</v>
       </c>
       <c r="B25" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3451,10 +2990,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>645895.5981272574</v>
+        <v>646072</v>
       </c>
       <c r="R25" t="n">
-        <v>7101955.561961574</v>
+        <v>7102013</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3484,19 +3023,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3523,37 +3052,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96497749</v>
+        <v>96497730</v>
       </c>
       <c r="B26" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3563,10 +3087,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>645865.8569030077</v>
+        <v>646045</v>
       </c>
       <c r="R26" t="n">
-        <v>7102074.067044117</v>
+        <v>7101949</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3596,21 +3120,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3619,11 +3133,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>kolad tallåga</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3640,37 +3149,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96497723</v>
+        <v>96497731</v>
       </c>
       <c r="B27" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3680,10 +3184,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646023.079291093</v>
+        <v>646028</v>
       </c>
       <c r="R27" t="n">
-        <v>7102069.142487677</v>
+        <v>7101923</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3713,21 +3217,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3736,11 +3230,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3757,37 +3246,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96497748</v>
+        <v>96497736</v>
       </c>
       <c r="B28" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3797,10 +3281,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>645859.8576514903</v>
+        <v>645929</v>
       </c>
       <c r="R28" t="n">
-        <v>7102070.71160253</v>
+        <v>7101925</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3830,19 +3314,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3869,37 +3343,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96497733</v>
+        <v>96497750</v>
       </c>
       <c r="B29" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3909,10 +3378,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>646016.1925558809</v>
+        <v>645873</v>
       </c>
       <c r="R29" t="n">
-        <v>7101915.979195877</v>
+        <v>7102105</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3942,21 +3411,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3965,11 +3424,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3986,15 +3440,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96497719</v>
+        <v>56824060</v>
       </c>
       <c r="B30" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4002,34 +3451,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>645992.7965990268</v>
+        <v>646092</v>
       </c>
       <c r="R30" t="n">
-        <v>7102086.606733845</v>
+        <v>7102196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4056,22 +3505,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4082,31 +3521,36 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>silverstubbe tall</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96497728</v>
+        <v>96497735</v>
       </c>
       <c r="B31" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4114,21 +3558,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4138,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>646058.2845145657</v>
+        <v>645943</v>
       </c>
       <c r="R31" t="n">
-        <v>7101984.27369022</v>
+        <v>7101926</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4171,21 +3615,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4194,6 +3628,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4210,50 +3649,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96497745</v>
+        <v>56824050</v>
       </c>
       <c r="B32" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>645858.4010591104</v>
+        <v>645893</v>
       </c>
       <c r="R32" t="n">
-        <v>7102026.724765424</v>
+        <v>7101903</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4280,22 +3714,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4307,35 +3731,35 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>kolad tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96497721</v>
+        <v>61489439</v>
       </c>
       <c r="B33" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,34 +3767,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>646023.079291093</v>
+        <v>646220</v>
       </c>
       <c r="R33" t="n">
-        <v>7102069.142487677</v>
+        <v>7102104</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4397,22 +3821,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4423,36 +3837,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+          <t>Per Nihlén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96497736</v>
+        <v>96497722</v>
       </c>
       <c r="B34" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4460,21 +3864,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4484,10 +3888,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>645928.7124320266</v>
+        <v>646023</v>
       </c>
       <c r="R34" t="n">
-        <v>7101924.613429351</v>
+        <v>7102069</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4517,21 +3921,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4540,6 +3934,11 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4556,37 +3955,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96497753</v>
+        <v>96497732</v>
       </c>
       <c r="B35" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4596,10 +3990,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>645911.5406255852</v>
+        <v>646016</v>
       </c>
       <c r="R35" t="n">
-        <v>7102112.660413449</v>
+        <v>7101916</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4629,21 +4023,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4652,6 +4036,11 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4668,15 +4057,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96497722</v>
+        <v>96497752</v>
       </c>
       <c r="B36" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4708,10 +4092,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>646023.079291093</v>
+        <v>645870</v>
       </c>
       <c r="R36" t="n">
-        <v>7102069.142487677</v>
+        <v>7102108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4741,19 +4125,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4785,15 +4159,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96497747</v>
+        <v>56824059</v>
       </c>
       <c r="B37" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4821,14 +4190,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>645861.8051343607</v>
+        <v>646072</v>
       </c>
       <c r="R37" t="n">
-        <v>7102076.073060833</v>
+        <v>7102170</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4855,22 +4224,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4882,57 +4241,57 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>kolad tallstubbe</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96497724</v>
+        <v>96497723</v>
       </c>
       <c r="B38" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4942,10 +4301,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>646037.1410556504</v>
+        <v>646023</v>
       </c>
       <c r="R38" t="n">
-        <v>7102069.363083259</v>
+        <v>7102069</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4975,21 +4334,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4998,6 +4347,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5014,37 +4368,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96497726</v>
+        <v>96497727</v>
       </c>
       <c r="B39" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5054,10 +4403,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>646059.011441518</v>
+        <v>646058</v>
       </c>
       <c r="R39" t="n">
-        <v>7102006.267611805</v>
+        <v>7102007</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5087,21 +4436,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5110,6 +4449,11 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5126,15 +4470,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96497718</v>
+        <v>96497734</v>
       </c>
       <c r="B40" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5142,21 +4481,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5166,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>645956.4946074472</v>
+        <v>645943</v>
       </c>
       <c r="R40" t="n">
-        <v>7102101.153768243</v>
+        <v>7101926</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5199,21 +4538,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5222,6 +4551,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5241,12 +4575,7 @@
         <v>96497744</v>
       </c>
       <c r="B41" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5278,10 +4607,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>645860.6771755951</v>
+        <v>645861</v>
       </c>
       <c r="R41" t="n">
-        <v>7102025.074678989</v>
+        <v>7102025</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5311,19 +4640,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5355,37 +4674,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96497720</v>
+        <v>96497747</v>
       </c>
       <c r="B42" t="n">
-        <v>86298</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>816</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5395,10 +4709,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>645985.5704854783</v>
+        <v>645862</v>
       </c>
       <c r="R42" t="n">
-        <v>7102090.65959615</v>
+        <v>7102076</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5428,21 +4742,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5451,6 +4755,11 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5467,15 +4776,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>96497750</v>
+        <v>96497751</v>
       </c>
       <c r="B43" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5483,21 +4787,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5507,10 +4811,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>645872.7560926189</v>
+        <v>645870</v>
       </c>
       <c r="R43" t="n">
-        <v>7102105.133013501</v>
+        <v>7102108</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5540,21 +4844,11 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5563,6 +4857,11 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5579,15 +4878,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>28046</v>
+        <v>56824053</v>
       </c>
       <c r="B44" t="n">
-        <v>57434</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,39 +4889,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100077</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oxvattenbäcken/Flärkån, Ås lm</t>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>646627.1147774999</v>
+        <v>645836</v>
       </c>
       <c r="R44" t="n">
-        <v>7101830.502308293</v>
+        <v>7101871</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5654,27 +4943,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Inventerare:Anders Karlsson, Jonatan Borling, spår</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5685,57 +4959,58 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Via Jonas F Grahn</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Inventering av utter Västerbottens län 2005-2007</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>61489428</v>
+        <v>56824057</v>
       </c>
       <c r="B45" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5745,10 +5020,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>646234.0599037252</v>
+        <v>646054</v>
       </c>
       <c r="R45" t="n">
-        <v>7102090.02809046</v>
+        <v>7102146</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5775,22 +5050,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5801,66 +5066,76 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>silverstubbe tall</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>61489439</v>
+        <v>28046</v>
       </c>
       <c r="B46" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100077</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Oxvattenbäcken/Flärkån, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>646220.2169401799</v>
+        <v>646627</v>
       </c>
       <c r="R46" t="n">
-        <v>7102103.870778368</v>
+        <v>7101831</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5887,22 +5162,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-08-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Inventerare:Anders Karlsson, Jonatan Borling, spår</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5917,27 +5187,26 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Via Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Inventering av utter Västerbottens län 2005-2007</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>61489440</v>
+        <v>56824051</v>
       </c>
       <c r="B47" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5945,21 +5214,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5969,10 +5238,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>646229.1650935733</v>
+        <v>645893</v>
       </c>
       <c r="R47" t="n">
-        <v>7102081.892758152</v>
+        <v>7101903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5999,22 +5268,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6025,31 +5284,36 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>61489441</v>
+        <v>56824052</v>
       </c>
       <c r="B48" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6057,21 +5321,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6081,10 +5345,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>646222.0736938291</v>
+        <v>645867</v>
       </c>
       <c r="R48" t="n">
-        <v>7102129.869724272</v>
+        <v>7101901</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6111,22 +5375,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6137,53 +5391,58 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>61489443</v>
+        <v>56824058</v>
       </c>
       <c r="B49" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6193,10 +5452,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>646187.1771745409</v>
+        <v>646072</v>
       </c>
       <c r="R49" t="n">
-        <v>7102123.83857958</v>
+        <v>7102170</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6223,22 +5482,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6249,66 +5498,71 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>61489444</v>
+        <v>96497721</v>
       </c>
       <c r="B50" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>646167.0418560723</v>
+        <v>646023</v>
       </c>
       <c r="R50" t="n">
-        <v>7102103.129697357</v>
+        <v>7102069</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6335,22 +5589,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6361,31 +5605,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>61489442</v>
+        <v>96497733</v>
       </c>
       <c r="B51" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6393,34 +5637,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>646221.0520162934</v>
+        <v>646016</v>
       </c>
       <c r="R51" t="n">
-        <v>7102132.895979558</v>
+        <v>7101916</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6447,22 +5691,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6473,31 +5707,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>62890461</v>
+        <v>56824056</v>
       </c>
       <c r="B52" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6505,21 +5739,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3100</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6529,10 +5763,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>646234.0599037252</v>
+        <v>646054</v>
       </c>
       <c r="R52" t="n">
-        <v>7102090.02809046</v>
+        <v>7102146</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6559,22 +5793,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6585,19 +5809,340 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>silverstubbe tall</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>56824061</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Flärkån-Oxvattenbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>646092</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7102196</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>silverstubbe tall</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>96497745</v>
+      </c>
+      <c r="B54" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>645858</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7102027</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>kolad tallåga</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>96497743</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Tallskogar vid Nilapiken-Råkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>645875</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7101997</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Anna Hallmén, Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33041-2024 artfynd.xlsx
+++ b/artfynd/A 33041-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6771509</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497720</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824049</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497749</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61489442</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497719</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497728</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497737</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497739</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497748</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1768,6 +1823,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62890461</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1865,6 +1925,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61489428</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1962,6 +2027,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61489443</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2059,6 +2129,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497724</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2156,6 +2231,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497726</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2253,6 +2333,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497741</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2350,6 +2435,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61489444</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2447,6 +2537,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497753</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2544,6 +2639,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61489441</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2651,6 +2751,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824048</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2758,6 +2863,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824055</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2855,6 +2965,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61489440</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2952,6 +3067,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497718</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3049,6 +3169,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497725</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3146,6 +3271,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497730</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3243,6 +3373,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497731</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3340,6 +3475,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497736</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3437,6 +3577,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497750</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3544,6 +3689,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824060</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3646,6 +3796,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497735</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3753,6 +3908,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824050</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3850,6 +4010,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61489439</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3952,6 +4117,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497722</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4054,6 +4224,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497732</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4156,6 +4331,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497752</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4263,6 +4443,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824059</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4365,6 +4550,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497723</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4467,6 +4657,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497727</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4569,6 +4764,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497734</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4671,6 +4871,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497744</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4773,6 +4978,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497747</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4875,6 +5085,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497751</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4982,6 +5197,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824053</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5089,6 +5309,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824057</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5200,6 +5425,11 @@
           <t>Inventering av utter Västerbottens län 2005-2007</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/28046</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5307,6 +5537,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824051</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5414,6 +5649,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824052</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5521,6 +5761,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824058</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5623,6 +5868,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497721</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5725,6 +5975,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497733</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5832,6 +6087,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824056</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5939,6 +6199,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56824061</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6041,6 +6306,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497745</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6143,8 +6413,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96497743</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>